--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.84676025135461</v>
+        <v>4.362598540845124</v>
       </c>
       <c r="D2" t="n">
-        <v>26.90430395936811</v>
+        <v>4.371949393397317</v>
       </c>
       <c r="E2" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F2" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.41979080243144</v>
+        <v>5.43071600539511</v>
       </c>
       <c r="D3" t="n">
-        <v>33.67546044349422</v>
+        <v>5.47226232206781</v>
       </c>
       <c r="E3" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F3" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.29046641951195</v>
+        <v>2.322200793170692</v>
       </c>
       <c r="D4" t="n">
-        <v>14.22272562328157</v>
+        <v>2.311192913783255</v>
       </c>
       <c r="E4" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F4" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.11395513129994</v>
+        <v>5.38101770883624</v>
       </c>
       <c r="D5" t="n">
-        <v>32.85031728378267</v>
+        <v>5.338176558614683</v>
       </c>
       <c r="E5" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F5" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.85956506210307</v>
+        <v>4.20217932259175</v>
       </c>
       <c r="D6" t="n">
-        <v>25.83636545897604</v>
+        <v>4.198409387083607</v>
       </c>
       <c r="E6" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F6" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.07275660568464</v>
+        <v>1.961822948423754</v>
       </c>
       <c r="D7" t="n">
-        <v>11.86302414534598</v>
+        <v>1.927741423618722</v>
       </c>
       <c r="E7" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F7" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.42263967283425</v>
+        <v>3.643678946835566</v>
       </c>
       <c r="D8" t="n">
-        <v>22.22605008986165</v>
+        <v>3.611733139602519</v>
       </c>
       <c r="E8" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F8" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.41026871337461</v>
+        <v>6.241668665923374</v>
       </c>
       <c r="D9" t="n">
-        <v>38.13501180280525</v>
+        <v>6.196939417955853</v>
       </c>
       <c r="E9" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F9" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>20.58537718083015</v>
+        <v>3.3451237918849</v>
       </c>
       <c r="D10" t="n">
-        <v>20.68113143854934</v>
+        <v>3.360683858764267</v>
       </c>
       <c r="E10" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F10" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.59567584893453</v>
+        <v>4.159297325451861</v>
       </c>
       <c r="D11" t="n">
-        <v>25.34296163654741</v>
+        <v>4.118231265938954</v>
       </c>
       <c r="E11" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F11" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.51302296611015</v>
+        <v>5.2833662319929</v>
       </c>
       <c r="D12" t="n">
-        <v>33.29025261929944</v>
+        <v>5.409666050636159</v>
       </c>
       <c r="E12" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F12" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>41.35316080335898</v>
+        <v>6.719888630545835</v>
       </c>
       <c r="D13" t="n">
-        <v>34.19151820781541</v>
+        <v>5.556121708770004</v>
       </c>
       <c r="E13" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F13" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>21.29641703261372</v>
+        <v>3.460667767799729</v>
       </c>
       <c r="D14" t="n">
-        <v>22.08329637387332</v>
+        <v>3.588535660754415</v>
       </c>
       <c r="E14" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F14" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>24.20743687382041</v>
+        <v>3.933708491995817</v>
       </c>
       <c r="D15" t="n">
-        <v>26.14368645633792</v>
+        <v>4.248349049154911</v>
       </c>
       <c r="E15" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F15" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>29.2959041505805</v>
+        <v>4.760584424469332</v>
       </c>
       <c r="D16" t="n">
-        <v>31.22699152976476</v>
+        <v>5.074386123586773</v>
       </c>
       <c r="E16" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F16" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>38.18473958947529</v>
+        <v>6.205020183289736</v>
       </c>
       <c r="D17" t="n">
-        <v>37.93382694212915</v>
+        <v>6.164246878095987</v>
       </c>
       <c r="E17" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F17" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34.73710756326357</v>
+        <v>5.64477997903033</v>
       </c>
       <c r="D18" t="n">
-        <v>33.65315758086337</v>
+        <v>5.468638106890298</v>
       </c>
       <c r="E18" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F18" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>42.16724765967438</v>
+        <v>6.852177744697087</v>
       </c>
       <c r="D19" t="n">
-        <v>43.66288836517867</v>
+        <v>7.095219359341534</v>
       </c>
       <c r="E19" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F19" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>28.91940845982831</v>
+        <v>4.6994038747221</v>
       </c>
       <c r="D20" t="n">
-        <v>24.74179346459406</v>
+        <v>4.020541437996535</v>
       </c>
       <c r="E20" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F20" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>11.92686044187656</v>
+        <v>1.938114821804942</v>
       </c>
       <c r="D21" t="n">
-        <v>12.21167474181981</v>
+        <v>1.98439714554572</v>
       </c>
       <c r="E21" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F21" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>45.08328177645517</v>
+        <v>7.326033288673965</v>
       </c>
       <c r="D22" t="n">
-        <v>45.75368492039691</v>
+        <v>7.434973799564498</v>
       </c>
       <c r="E22" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F22" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>1.183222360827094</v>
+        <v>0.1922736336344028</v>
       </c>
       <c r="D23" t="n">
-        <v>9.183163342112461</v>
+        <v>1.492264043093275</v>
       </c>
       <c r="E23" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F23" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>38.99679313862573</v>
+        <v>6.336978885026681</v>
       </c>
       <c r="D24" t="n">
-        <v>39.01004133442081</v>
+        <v>6.339131716843381</v>
       </c>
       <c r="E24" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F24" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>20.50632154547152</v>
+        <v>3.332277251139122</v>
       </c>
       <c r="D25" t="n">
-        <v>16.65193674739798</v>
+        <v>2.705939721452172</v>
       </c>
       <c r="E25" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F25" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>17.9009367265125</v>
+        <v>2.908902218058281</v>
       </c>
       <c r="D26" t="n">
-        <v>21.76155683021853</v>
+        <v>3.536252984910512</v>
       </c>
       <c r="E26" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F26" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>35.98882283518067</v>
+        <v>5.848183710716859</v>
       </c>
       <c r="D27" t="n">
-        <v>35.80642577800044</v>
+        <v>5.818544188925071</v>
       </c>
       <c r="E27" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F27" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>13.13296053589867</v>
+        <v>2.134106087083535</v>
       </c>
       <c r="D28" t="n">
-        <v>16.81462683966219</v>
+        <v>2.732376861445106</v>
       </c>
       <c r="E28" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F28" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>26.31111549406149</v>
+        <v>4.275556267784991</v>
       </c>
       <c r="D29" t="n">
-        <v>26.53366787631447</v>
+        <v>4.311721029901102</v>
       </c>
       <c r="E29" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F29" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>33.04783777155147</v>
+        <v>5.370273637877114</v>
       </c>
       <c r="D30" t="n">
-        <v>33.40233026277058</v>
+        <v>5.42787866770022</v>
       </c>
       <c r="E30" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F30" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>21.85466053129288</v>
+        <v>3.551382336335092</v>
       </c>
       <c r="D31" t="n">
-        <v>22.20781762007796</v>
+        <v>3.60877036326267</v>
       </c>
       <c r="E31" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F31" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>30.20969055302526</v>
+        <v>4.909074714866605</v>
       </c>
       <c r="D32" t="n">
-        <v>30.55075614277432</v>
+        <v>4.964497873200828</v>
       </c>
       <c r="E32" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F32" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>20.44031426208177</v>
+        <v>3.321551067588287</v>
       </c>
       <c r="D33" t="n">
-        <v>20.13945881815459</v>
+        <v>3.272662057950121</v>
       </c>
       <c r="E33" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F33" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>36.13559113168848</v>
+        <v>5.872033558899378</v>
       </c>
       <c r="D34" t="n">
-        <v>36.46393719635501</v>
+        <v>5.92538979440769</v>
       </c>
       <c r="E34" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F34" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>46.04270573850796</v>
+        <v>7.481939682507544</v>
       </c>
       <c r="D35" t="n">
-        <v>46.35815147198453</v>
+        <v>7.533199614197487</v>
       </c>
       <c r="E35" t="n">
-        <v>10.38225659679019</v>
+        <v>1.687116696978406</v>
       </c>
       <c r="F35" t="n">
-        <v>9.618649714043599</v>
+        <v>1.563030578532085</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
